--- a/physician_forms/006_first_aid_treatment_form--physician_forms.xlsx
+++ b/physician_forms/006_first_aid_treatment_form--physician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,8 +619,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'treatment_date',_'label':_'treatment_date',_'type':_'date',_'options':_[],_'required':_true}</t>
+          <t>treatment_date</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'treatment_date', 'label': 'Treatment Date', 'type': 'date', 'options': [], 'required': True}</t>
+          <t>Treatment Date</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'treatment_location',_'label':_'treatment_location',_'type':_'text',_'options':_[],_'required':_true}</t>
+          <t>treatment_location</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'treatment_location', 'label': 'Treatment Location', 'type': 'text', 'options': [], 'required': True}</t>
+          <t>Treatment Location</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'symptoms',_'label':_'symptoms',_'type':_'text',_'options':_[],_'required':_true}</t>
+          <t>symptoms</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'symptoms', 'label': 'Symptoms', 'type': 'text', 'options': [], 'required': True}</t>
+          <t>Symptoms</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'patient_notes',_'label':_'patient_notes',_'type':_'text',_'options':_[],_'required':_false}</t>
+          <t>patient_notes</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'patient_notes', 'label': 'Patient Notes', 'type': 'text', 'options': [], 'required': False}</t>
+          <t>Patient Notes</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'physician_name',_'label':_'physician_name',_'type':_'text',_'options':_[],_'required':_true}</t>
+          <t>physician_name</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'physician_name', 'label': 'Physician Name', 'type': 'text', 'options': [], 'required': True}</t>
+          <t>Physician Name</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'physician_phone',_'label':_'physician_phone',_'type':_'phone',_'options':_[],_'required':_true}</t>
+          <t>physician_phone</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'physician_phone', 'label': 'Physician Phone', 'type': 'phone', 'options': [], 'required': True}</t>
+          <t>Physician Phone</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'physician_email',_'label':_'physician_email',_'type':_'email',_'options':_[],_'required':_true}</t>
+          <t>physician_email</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'physician_email', 'label': 'Physician Email', 'type': 'email', 'options': [], 'required': True}</t>
+          <t>Physician Email</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'physician_notes',_'label':_'physician_notes',_'type':_'text',_'options':_[],_'required':_false}</t>
+          <t>physician_notes</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'physician_notes', 'label': 'Physician Notes', 'type': 'text', 'options': [], 'required': False}</t>
+          <t>Physician Notes</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'medical_record_number',_'label':_'medical_record_number',_'type':_'text',_'options':_[],_'required':_true}</t>
+          <t>medical_record_number</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'medical_record_number', 'label': 'Medical Record Number', 'type': 'text', 'options': [], 'required': True}</t>
+          <t>Medical Record Number</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'medical_provider',_'label':_'medical_provider',_'type':_'select_one',_'options':_['emergency_room',_'nurse',_'physician_assistant',_'physician',_'surgeon'],_'required':_true}</t>
+          <t>medical_provider</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'medical_provider', 'label': 'Medical Provider', 'type': 'select_one', 'options': ['Emergency Room', 'Nurse', 'Physician Assistant', 'Physician', 'Surgeon'], 'required': True}</t>
+          <t>Medical Provider</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'patient_medical_history',_'label':_'patient_medical_history',_'type':_'date',_'options':_[],_'required':_true}</t>
+          <t>patient_medical_history</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'patient_medical_history', 'label': 'Patient Medical History', 'type': 'date', 'options': [], 'required': True}</t>
+          <t>Patient Medical History</t>
         </is>
       </c>
     </row>
